--- a/251211/NMDAR_antibody.xlsx
+++ b/251211/NMDAR_antibody.xlsx
@@ -383,11 +383,11 @@
         </is>
       </c>
       <c r="B2">
-        <v>1.0225</v>
+        <v>1.2488</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.0045 – 1.0412</t>
+          <t>1.0456 – 1.4974</t>
         </is>
       </c>
       <c r="D2">
@@ -401,11 +401,11 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.016</v>
+        <v>1.1718</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.9995 – 1.0331</t>
+          <t>0.9947 – 1.3843</t>
         </is>
       </c>
       <c r="D3">
@@ -419,11 +419,11 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.0191</v>
+        <v>1.2087</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.0035 – 1.0354</t>
+          <t>1.0354 – 1.4166</t>
         </is>
       </c>
       <c r="D4">
@@ -437,11 +437,11 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.0084</v>
+        <v>1.0878</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.9936 – 1.0236</t>
+          <t>0.9381 – 1.2631</t>
         </is>
       </c>
       <c r="D5">
@@ -455,11 +455,11 @@
         </is>
       </c>
       <c r="B6">
-        <v>11.465</v>
+        <v>1.2763</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.5655 – 54.0665</t>
+          <t>1.0988 – 1.4904</t>
         </is>
       </c>
       <c r="D6">
@@ -473,11 +473,11 @@
         </is>
       </c>
       <c r="B7">
-        <v>6.5457</v>
+        <v>1.2067</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.6728 – 27.4501</t>
+          <t>1.0528 – 1.3927</t>
         </is>
       </c>
       <c r="D7">
@@ -491,11 +491,11 @@
         </is>
       </c>
       <c r="B8">
-        <v>4.6959</v>
+        <v>1.1673</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.3069 – 17.7326</t>
+          <t>1.0271 – 1.3331</t>
         </is>
       </c>
       <c r="D8">
@@ -509,11 +509,11 @@
         </is>
       </c>
       <c r="B9">
-        <v>2.82</v>
+        <v>1.1092</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.8277 – 9.9379</t>
+          <t>0.9813 – 1.2581</t>
         </is>
       </c>
       <c r="D9">
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="B10">
-        <v>1.0187</v>
+        <v>1.2034</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.9986 – 1.0395</t>
+          <t>0.9862 – 1.4731</t>
         </is>
       </c>
       <c r="D10">
@@ -545,11 +545,11 @@
         </is>
       </c>
       <c r="B11">
-        <v>1.015</v>
+        <v>1.1602</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.9964 – 1.0341</t>
+          <t>0.9649 – 1.3988</t>
         </is>
       </c>
       <c r="D11">
@@ -563,11 +563,11 @@
         </is>
       </c>
       <c r="B12">
-        <v>1.0169</v>
+        <v>1.1824</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.9989 – 1.0355</t>
+          <t>0.9895 – 1.4177</t>
         </is>
       </c>
       <c r="D12">
@@ -581,11 +581,11 @@
         </is>
       </c>
       <c r="B13">
-        <v>1.0029</v>
+        <v>1.0293</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.9861 – 1.02</t>
+          <t>0.8695 – 1.2192</t>
         </is>
       </c>
       <c r="D13">
@@ -599,11 +599,11 @@
         </is>
       </c>
       <c r="B14">
-        <v>1.0005</v>
+        <v>1.0048</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.9863 – 1.0149</t>
+          <t>0.8708 – 1.1595</t>
         </is>
       </c>
       <c r="D14">
@@ -617,11 +617,11 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.9892</v>
+        <v>0.897</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.9734 – 1.005</t>
+          <t>0.7634 – 1.0514</t>
         </is>
       </c>
       <c r="D15">
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="B16">
-        <v>1.0035</v>
+        <v>1.0351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.9889 – 1.0183</t>
+          <t>0.8948 – 1.1986</t>
         </is>
       </c>
       <c r="D16">
@@ -653,11 +653,11 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.9926</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.9783 – 1.007</t>
+          <t>0.8028 – 1.0726</t>
         </is>
       </c>
       <c r="D17">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="B18">
-        <v>1.0197</v>
+        <v>1.2153</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.0044 – 1.0356</t>
+          <t>1.0448 – 1.4188</t>
         </is>
       </c>
       <c r="D18">
@@ -689,11 +689,11 @@
         </is>
       </c>
       <c r="B19">
-        <v>1.016</v>
+        <v>1.1725</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.002 – 1.0306</t>
+          <t>1.0201 – 1.3518</t>
         </is>
       </c>
       <c r="D19">
@@ -707,11 +707,11 @@
         </is>
       </c>
       <c r="B20">
-        <v>1.0197</v>
+        <v>1.2152</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.0058 – 1.0342</t>
+          <t>1.0596 – 1.3992</t>
         </is>
       </c>
       <c r="D20">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="B21">
-        <v>1.0092</v>
+        <v>1.0957</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.9962 – 1.0225</t>
+          <t>0.9627 – 1.2489</t>
         </is>
       </c>
       <c r="D21">
@@ -743,11 +743,11 @@
         </is>
       </c>
       <c r="B22">
-        <v>1.0293</v>
+        <v>1.3348</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.0067 – 1.053</t>
+          <t>1.0691 – 1.6754</t>
         </is>
       </c>
       <c r="D22">
@@ -761,11 +761,11 @@
         </is>
       </c>
       <c r="B23">
-        <v>1.0212</v>
+        <v>1.2335</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.0007 – 1.0426</t>
+          <t>1.0066 – 1.5174</t>
         </is>
       </c>
       <c r="D23">
@@ -779,11 +779,11 @@
         </is>
       </c>
       <c r="B24">
-        <v>1.0228</v>
+        <v>1.2531</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.0039 – 1.0426</t>
+          <t>1.0395 – 1.518</t>
         </is>
       </c>
       <c r="D24">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="B25">
-        <v>1.0143</v>
+        <v>1.1528</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.9962 – 1.033</t>
+          <t>0.9627 – 1.384</t>
         </is>
       </c>
       <c r="D25">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="B26">
-        <v>1.0194</v>
+        <v>1.212</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.0042 – 1.0353</t>
+          <t>1.0424 – 1.4142</t>
         </is>
       </c>
       <c r="D26">
@@ -833,11 +833,11 @@
         </is>
       </c>
       <c r="B27">
-        <v>1.0158</v>
+        <v>1.1701</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.0018 – 1.0303</t>
+          <t>1.0185 – 1.3482</t>
         </is>
       </c>
       <c r="D27">
@@ -851,11 +851,11 @@
         </is>
       </c>
       <c r="B28">
-        <v>1.0193</v>
+        <v>1.2102</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.0055 – 1.0337</t>
+          <t>1.0559 – 1.3924</t>
         </is>
       </c>
       <c r="D28">
@@ -869,11 +869,11 @@
         </is>
       </c>
       <c r="B29">
-        <v>1.0094</v>
+        <v>1.0983</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.9964 – 1.0227</t>
+          <t>0.965 – 1.2521</t>
         </is>
       </c>
       <c r="D29">
